--- a/E/KLIKN.xlsx
+++ b/E/KLIKN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -430,17 +430,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,6 +458,12 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -477,7 +484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -493,7 +500,7 @@
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/E/KLIKN.xlsx
+++ b/E/KLIKN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -430,18 +430,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,12 +457,6 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -484,7 +477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -500,7 +493,7 @@
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
